--- a/content/test/data/dance-schedule.xlsx
+++ b/content/test/data/dance-schedule.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>Time</t>
   </si>
@@ -24,6 +24,9 @@
   </si>
   <si>
     <t>Test Room C</t>
+  </si>
+  <si>
+    <t>Test Room D</t>
   </si>
   <si>
     <t>9:00a-10:00a</t>
@@ -59,6 +62,12 @@
   <si>
     <t xml:space="preserve">C1 &amp; C2 : Dancing - Test Caller Four
 GCA: Test GCA Person</t>
+  </si>
+  <si>
+    <t>9:00a-12:00p</t>
+  </si>
+  <si>
+    <t>Plus : Long Workshop - Test Caller Eight</t>
   </si>
   <si>
     <t>9:00a-10:30a</t>
@@ -454,10 +463,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -470,53 +479,64 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -536,32 +556,32 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/content/test/data/dance-schedule.xlsx
+++ b/content/test/data/dance-schedule.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
   <si>
     <t>Time</t>
   </si>
@@ -27,6 +27,12 @@
   </si>
   <si>
     <t>Test Room D</t>
+  </si>
+  <si>
+    <t>The Grand Overflow Annex Ballroom</t>
+  </si>
+  <si>
+    <t>Gym</t>
   </si>
   <si>
     <t>9:00a-10:00a</t>
@@ -70,6 +76,65 @@
     <t>Plus : Long Workshop - Test Caller Eight</t>
   </si>
   <si>
+    <t>12:30p-1:30p</t>
+  </si>
+  <si>
+    <t>Plus : Dancing - Test Caller One &amp; Test Caller Two &amp; Zed</t>
+  </si>
+  <si>
+    <t>1:00p-2:00p</t>
+  </si>
+  <si>
+    <t>SSD : Dancing - François Côté</t>
+  </si>
+  <si>
+    <t>C2 : Dancing - Alexander Bartholomew Fitzgerald-Montgomery</t>
+  </si>
+  <si>
+    <t>SSD : Dancing - Test Caller Three</t>
+  </si>
+  <si>
+    <t>C4 : Dancing - Test Caller Four</t>
+  </si>
+  <si>
+    <t>2:00p-3:00p</t>
+  </si>
+  <si>
+    <t>MS : Dancing - Björn Åström</t>
+  </si>
+  <si>
+    <t>3:00p-4:00p</t>
+  </si>
+  <si>
+    <t>A1 : Dancing - Zed</t>
+  </si>
+  <si>
+    <t>C1 : Advanced Choreography Workshop: Exploring Symmetric and Asymmetric Formations in Western Square Dance Technique - Test Caller Five</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4 : Dancing - Test Caller Seven
+GCA: François Côté</t>
+  </si>
+  <si>
+    <t>4:00p-5:00p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS : Big Group Dance - Alexander Bartholomew Fitzgerald-Montgomery
+ROOMS: Test Room A, Test Room D</t>
+  </si>
+  <si>
+    <t>7:00a-9:00a</t>
+  </si>
+  <si>
+    <t>SSD : Dancing - Zed</t>
+  </si>
+  <si>
+    <t>7:00a-9:30a</t>
+  </si>
+  <si>
+    <t>MS : Dancing - François Côté</t>
+  </si>
+  <si>
     <t>9:00a-10:30a</t>
   </si>
   <si>
@@ -81,9 +146,6 @@
   <si>
     <t xml:space="preserve">* Snack Break
 ROOMS: NONE</t>
-  </si>
-  <si>
-    <t>2:00p-3:00p</t>
   </si>
   <si>
     <t>MS : Dancing - Test Caller Seven</t>
@@ -463,10 +525,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -482,56 +544,158 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -558,26 +722,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
